--- a/main/ig/StructureDefinition-fr-cda-dicom-quantite-subordonnee.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-dicom-quantite-subordonnee.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T09:33:49+00:00</t>
+    <t>2026-03-30T15:11:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-dicom-quantite-subordonnee.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-dicom-quantite-subordonnee.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T15:11:58+00:00</t>
+    <t>2026-03-31T07:16:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-dicom-quantite-subordonnee.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-dicom-quantite-subordonnee.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T07:16:03+00:00</t>
+    <t>2026-04-01T07:43:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-dicom-quantite-subordonnee.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-dicom-quantite-subordonnee.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T07:43:12+00:00</t>
+    <t>2026-04-02T07:21:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-dicom-quantite-subordonnee.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-dicom-quantite-subordonnee.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T07:21:27+00:00</t>
+    <t>2026-04-02T12:41:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-dicom-quantite-subordonnee.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-dicom-quantite-subordonnee.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T12:41:19+00:00</t>
+    <t>2026-04-07T08:23:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-dicom-quantite-subordonnee.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-dicom-quantite-subordonnee.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-snapsnot</t>
+    <t>0.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T08:23:13+00:00</t>
+    <t>2026-04-15T13:29:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-dicom-quantite-subordonnee.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-dicom-quantite-subordonnee.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T13:29:57+00:00</t>
+    <t>2026-04-15T15:41:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-dicom-quantite-subordonnee.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-dicom-quantite-subordonnee.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$110</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3133" uniqueCount="345">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3482" uniqueCount="356">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T15:41:19+00:00</t>
+    <t>2026-04-20T15:11:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -520,6 +520,132 @@
     <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-quantite-exposition-rayonnements-cisis</t>
   </si>
   <si>
+    <t>Observation.code.nullFlavor</t>
+  </si>
+  <si>
+    <t>Observation.code.code</t>
+  </si>
+  <si>
+    <t>The plain code symbol defined by the code system. For example, "784.0" is the code symbol of the ICD-9 code "784.0" for headache.</t>
+  </si>
+  <si>
+    <t>CD.code</t>
+  </si>
+  <si>
+    <t>Observation.code.codeSystem</t>
+  </si>
+  <si>
+    <t>Code System</t>
+  </si>
+  <si>
+    <t>Specifies the code system that defines the code.</t>
+  </si>
+  <si>
+    <t>CD.codeSystem</t>
+  </si>
+  <si>
+    <t>Observation.code.codeSystemName</t>
+  </si>
+  <si>
+    <t>Code System Name</t>
+  </si>
+  <si>
+    <t>The common name of the coding system.</t>
+  </si>
+  <si>
+    <t>CD.codeSystemName</t>
+  </si>
+  <si>
+    <t>Observation.code.codeSystemVersion</t>
+  </si>
+  <si>
+    <t>Code System Version</t>
+  </si>
+  <si>
+    <t>If applicable, a version descriptor defined specifically for the given code system.</t>
+  </si>
+  <si>
+    <t>CD.codeSystemVersion</t>
+  </si>
+  <si>
+    <t>Observation.code.displayName</t>
+  </si>
+  <si>
+    <t>Display Name</t>
+  </si>
+  <si>
+    <t>A name or title for the code, under which the sending system shows the code value to its users.</t>
+  </si>
+  <si>
+    <t>CD.displayName</t>
+  </si>
+  <si>
+    <t>Observation.code.sdtcValueSet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string {http://hl7.org/cda/stds/core/StructureDefinition/oid}
+</t>
+  </si>
+  <si>
+    <t>The valueSet extension adds an attribute for elements with a CD dataType which indicates the particular value set constraining the coded concept.</t>
+  </si>
+  <si>
+    <t>CD.valueSet</t>
+  </si>
+  <si>
+    <t>Observation.code.sdtcValueSetVersion</t>
+  </si>
+  <si>
+    <t>The valueSetVersion extension adds an attribute for elements with a CD dataType which indicates the version of the particular value set constraining the coded concept.</t>
+  </si>
+  <si>
+    <t>CD.sdtcValueSetVersion</t>
+  </si>
+  <si>
+    <t>Observation.code.originalText</t>
+  </si>
+  <si>
+    <t>Original Text</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/ED
+</t>
+  </si>
+  <si>
+    <t>The text or phrase used as the basis for the coding.</t>
+  </si>
+  <si>
+    <t>CD.originalText</t>
+  </si>
+  <si>
+    <t>Observation.code.qualifier</t>
+  </si>
+  <si>
+    <t>Qualifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/CR
+</t>
+  </si>
+  <si>
+    <t>Specifies additional codes that increase the specificity of the the primary code.</t>
+  </si>
+  <si>
+    <t>CD.qualifier</t>
+  </si>
+  <si>
+    <t>Observation.code.translation</t>
+  </si>
+  <si>
+    <t>Translation</t>
+  </si>
+  <si>
+    <t>A set of other concept descriptors that translate this concept descriptor into other code systems.</t>
+  </si>
+  <si>
+    <t>CD.translation</t>
+  </si>
+  <si>
     <t>Observation.derivationExpr</t>
   </si>
   <si>
@@ -530,10 +656,6 @@
     <t>Observation.text</t>
   </si>
   <si>
-    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/ED
-</t>
-  </si>
-  <si>
     <t>Partie narrative de l'entrée</t>
   </si>
   <si>
@@ -750,108 +872,31 @@
     <t>Observation.targetSiteCode.code</t>
   </si>
   <si>
-    <t>The plain code symbol defined by the code system. For example, "784.0" is the code symbol of the ICD-9 code "784.0" for headache.</t>
-  </si>
-  <si>
-    <t>CD.code</t>
-  </si>
-  <si>
     <t>Observation.targetSiteCode.codeSystem</t>
   </si>
   <si>
-    <t>Code System</t>
-  </si>
-  <si>
-    <t>Specifies the code system that defines the code.</t>
-  </si>
-  <si>
-    <t>CD.codeSystem</t>
-  </si>
-  <si>
     <t>Observation.targetSiteCode.codeSystemName</t>
   </si>
   <si>
-    <t>Code System Name</t>
-  </si>
-  <si>
-    <t>The common name of the coding system.</t>
-  </si>
-  <si>
-    <t>CD.codeSystemName</t>
-  </si>
-  <si>
     <t>Observation.targetSiteCode.codeSystemVersion</t>
   </si>
   <si>
-    <t>Code System Version</t>
-  </si>
-  <si>
-    <t>If applicable, a version descriptor defined specifically for the given code system.</t>
-  </si>
-  <si>
-    <t>CD.codeSystemVersion</t>
-  </si>
-  <si>
     <t>Observation.targetSiteCode.displayName</t>
   </si>
   <si>
-    <t>Display Name</t>
-  </si>
-  <si>
-    <t>A name or title for the code, under which the sending system shows the code value to its users.</t>
-  </si>
-  <si>
-    <t>CD.displayName</t>
-  </si>
-  <si>
     <t>Observation.targetSiteCode.sdtcValueSet</t>
   </si>
   <si>
-    <t xml:space="preserve">string {http://hl7.org/cda/stds/core/StructureDefinition/oid}
-</t>
-  </si>
-  <si>
-    <t>The valueSet extension adds an attribute for elements with a CD dataType which indicates the particular value set constraining the coded concept.</t>
-  </si>
-  <si>
-    <t>CD.valueSet</t>
-  </si>
-  <si>
     <t>Observation.targetSiteCode.sdtcValueSetVersion</t>
   </si>
   <si>
-    <t>The valueSetVersion extension adds an attribute for elements with a CD dataType which indicates the version of the particular value set constraining the coded concept.</t>
-  </si>
-  <si>
-    <t>CD.sdtcValueSetVersion</t>
-  </si>
-  <si>
     <t>Observation.targetSiteCode.originalText</t>
   </si>
   <si>
-    <t>Original Text</t>
-  </si>
-  <si>
-    <t>The text or phrase used as the basis for the coding.</t>
-  </si>
-  <si>
-    <t>CD.originalText</t>
-  </si>
-  <si>
     <t>Observation.targetSiteCode.qualifier</t>
   </si>
   <si>
-    <t>Qualifier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/CR
-</t>
-  </si>
-  <si>
     <t>Topographie</t>
-  </si>
-  <si>
-    <t>CD.qualifier</t>
   </si>
   <si>
     <t>Observation.targetSiteCode.qualifier.nullFlavor</t>
@@ -928,19 +973,7 @@
     <t>Observation.targetSiteCode.qualifier.name.qualifier</t>
   </si>
   <si>
-    <t>Specifies additional codes that increase the specificity of the the primary code.</t>
-  </si>
-  <si>
     <t>Observation.targetSiteCode.qualifier.name.translation</t>
-  </si>
-  <si>
-    <t>Translation</t>
-  </si>
-  <si>
-    <t>A set of other concept descriptors that translate this concept descriptor into other code systems.</t>
-  </si>
-  <si>
-    <t>CD.translation</t>
   </si>
   <si>
     <t>Observation.targetSiteCode.qualifier.value</t>
@@ -1402,7 +1435,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK99"/>
+  <dimension ref="A1:AK110"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="63.44140625" customWidth="true" bestFit="true"/>
@@ -4103,7 +4136,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
         <v>157</v>
       </c>
@@ -4122,7 +4155,7 @@
         <v>75</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>74</v>
@@ -4417,7 +4450,9 @@
       <c r="D30" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E30" s="2"/>
+      <c r="E30" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F30" t="s" s="2">
         <v>80</v>
       </c>
@@ -4434,10 +4469,12 @@
         <v>74</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>165</v>
+        <v>85</v>
       </c>
       <c r="L30" s="2"/>
-      <c r="M30" s="2"/>
+      <c r="M30" t="s" s="2">
+        <v>86</v>
+      </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -4463,13 +4500,11 @@
         <v>74</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y30" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y30" s="2"/>
       <c r="Z30" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>74</v>
@@ -4487,7 +4522,7 @@
         <v>74</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>164</v>
+        <v>89</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -4507,18 +4542,20 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E31" s="2"/>
+      <c r="E31" t="s" s="2">
+        <v>62</v>
+      </c>
       <c r="F31" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>75</v>
@@ -4533,13 +4570,11 @@
         <v>74</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="L31" t="s" s="2">
-        <v>168</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="L31" s="2"/>
       <c r="M31" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4590,7 +4625,7 @@
         <v>74</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -4608,28 +4643,28 @@
         <v>74</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E32" t="s" s="2">
-        <v>84</v>
+        <v>169</v>
       </c>
       <c r="F32" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>74</v>
@@ -4638,11 +4673,11 @@
         <v>74</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>85</v>
+        <v>112</v>
       </c>
       <c r="L32" s="2"/>
       <c r="M32" t="s" s="2">
-        <v>86</v>
+        <v>170</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4669,11 +4704,13 @@
         <v>74</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y32" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y32" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z32" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>74</v>
@@ -4691,7 +4728,7 @@
         <v>74</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>89</v>
+        <v>171</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -4711,17 +4748,17 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E33" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="F33" t="s" s="2">
         <v>80</v>
@@ -4739,11 +4776,11 @@
         <v>74</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="L33" s="2"/>
       <c r="M33" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4770,11 +4807,13 @@
         <v>74</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y33" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y33" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z33" t="s" s="2">
-        <v>173</v>
+        <v>74</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>74</v>
@@ -4792,7 +4831,7 @@
         <v>74</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -4812,17 +4851,17 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E34" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F34" t="s" s="2">
         <v>80</v>
@@ -4840,7 +4879,7 @@
         <v>74</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>177</v>
+        <v>102</v>
       </c>
       <c r="L34" s="2"/>
       <c r="M34" t="s" s="2">
@@ -4913,7 +4952,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="35" hidden="true">
+    <row r="35">
       <c r="A35" t="s" s="2">
         <v>180</v>
       </c>
@@ -4934,7 +4973,7 @@
         <v>75</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>74</v>
@@ -4943,7 +4982,7 @@
         <v>74</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="L35" s="2"/>
       <c r="M35" t="s" s="2">
@@ -4974,29 +5013,31 @@
         <v>74</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y35" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y35" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF35" t="s" s="2">
         <v>183</v>
-      </c>
-      <c r="AA35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF35" t="s" s="2">
-        <v>184</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -5016,18 +5057,16 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E36" t="s" s="2">
-        <v>186</v>
-      </c>
+      <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>80</v>
       </c>
@@ -5044,11 +5083,11 @@
         <v>74</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>85</v>
+        <v>185</v>
       </c>
       <c r="L36" s="2"/>
       <c r="M36" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5099,7 +5138,7 @@
         <v>74</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -5119,18 +5158,16 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E37" t="s" s="2">
-        <v>190</v>
-      </c>
+      <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>80</v>
       </c>
@@ -5147,11 +5184,11 @@
         <v>74</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="L37" s="2"/>
       <c r="M37" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5178,11 +5215,13 @@
         <v>74</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="Y37" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y37" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z37" t="s" s="2">
-        <v>193</v>
+        <v>74</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>74</v>
@@ -5200,7 +5239,7 @@
         <v>74</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -5220,16 +5259,18 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E38" s="2"/>
+      <c r="E38" t="s" s="2">
+        <v>192</v>
+      </c>
       <c r="F38" t="s" s="2">
         <v>80</v>
       </c>
@@ -5246,10 +5287,12 @@
         <v>74</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>85</v>
+        <v>193</v>
       </c>
       <c r="L38" s="2"/>
-      <c r="M38" s="2"/>
+      <c r="M38" t="s" s="2">
+        <v>194</v>
+      </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -5275,11 +5318,13 @@
         <v>74</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y38" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y38" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z38" t="s" s="2">
-        <v>196</v>
+        <v>74</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>74</v>
@@ -5297,7 +5342,7 @@
         <v>74</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -5317,21 +5362,23 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E39" s="2"/>
+      <c r="E39" t="s" s="2">
+        <v>197</v>
+      </c>
       <c r="F39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>74</v>
@@ -5343,17 +5390,13 @@
         <v>74</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="L39" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="L39" s="2"/>
+      <c r="M39" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="M39" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>201</v>
-      </c>
+      <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>74</v>
@@ -5402,13 +5445,13 @@
         <v>74</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>74</v>
@@ -5420,28 +5463,28 @@
         <v>74</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E40" t="s" s="2">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="F40" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>151</v>
+        <v>74</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>74</v>
@@ -5450,11 +5493,11 @@
         <v>74</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>205</v>
+        <v>160</v>
       </c>
       <c r="L40" s="2"/>
       <c r="M40" t="s" s="2">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5505,13 +5548,13 @@
         <v>74</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>74</v>
@@ -5525,18 +5568,16 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E41" t="s" s="2">
-        <v>209</v>
-      </c>
+      <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>80</v>
       </c>
@@ -5553,12 +5594,10 @@
         <v>74</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>167</v>
+        <v>206</v>
       </c>
       <c r="L41" s="2"/>
-      <c r="M41" t="s" s="2">
-        <v>210</v>
-      </c>
+      <c r="M41" s="2"/>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -5608,7 +5647,7 @@
         <v>74</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -5628,10 +5667,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5639,7 +5678,7 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
         <v>75</v>
@@ -5654,13 +5693,13 @@
         <v>74</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>91</v>
+        <v>193</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5687,11 +5726,13 @@
         <v>74</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y42" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y42" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z42" t="s" s="2">
-        <v>214</v>
+        <v>74</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>74</v>
@@ -5709,7 +5750,7 @@
         <v>74</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -5727,18 +5768,20 @@
         <v>74</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E43" s="2"/>
+      <c r="E43" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F43" t="s" s="2">
         <v>80</v>
       </c>
@@ -5746,7 +5789,7 @@
         <v>75</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>151</v>
+        <v>74</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>74</v>
@@ -5755,13 +5798,11 @@
         <v>74</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="L43" t="s" s="2">
-        <v>217</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="L43" s="2"/>
       <c r="M43" t="s" s="2">
-        <v>217</v>
+        <v>86</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -5788,13 +5829,11 @@
         <v>74</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y43" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y43" s="2"/>
       <c r="Z43" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>74</v>
@@ -5812,7 +5851,7 @@
         <v>74</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>215</v>
+        <v>89</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -5832,16 +5871,18 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E44" s="2"/>
+      <c r="E44" t="s" s="2">
+        <v>211</v>
+      </c>
       <c r="F44" t="s" s="2">
         <v>80</v>
       </c>
@@ -5858,10 +5899,12 @@
         <v>74</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>219</v>
+        <v>85</v>
       </c>
       <c r="L44" s="2"/>
-      <c r="M44" s="2"/>
+      <c r="M44" t="s" s="2">
+        <v>212</v>
+      </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -5887,11 +5930,11 @@
         <v>74</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>192</v>
+        <v>87</v>
       </c>
       <c r="Y44" s="2"/>
       <c r="Z44" t="s" s="2">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>74</v>
@@ -5909,7 +5952,7 @@
         <v>74</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -5929,16 +5972,18 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E45" s="2"/>
+      <c r="E45" t="s" s="2">
+        <v>216</v>
+      </c>
       <c r="F45" t="s" s="2">
         <v>80</v>
       </c>
@@ -5955,10 +6000,12 @@
         <v>74</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="L45" s="2"/>
-      <c r="M45" s="2"/>
+      <c r="M45" t="s" s="2">
+        <v>218</v>
+      </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -6008,7 +6055,7 @@
         <v>74</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -6028,16 +6075,18 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E46" s="2"/>
+      <c r="E46" t="s" s="2">
+        <v>221</v>
+      </c>
       <c r="F46" t="s" s="2">
         <v>80</v>
       </c>
@@ -6054,10 +6103,12 @@
         <v>74</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="L46" s="2"/>
-      <c r="M46" s="2"/>
+      <c r="M46" t="s" s="2">
+        <v>222</v>
+      </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6087,26 +6138,26 @@
       </c>
       <c r="Y46" s="2"/>
       <c r="Z46" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="AA46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF46" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="AA46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF46" t="s" s="2">
-        <v>223</v>
-      </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
       </c>
@@ -6123,7 +6174,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
         <v>225</v>
       </c>
@@ -6134,15 +6185,17 @@
       <c r="D47" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E47" s="2"/>
+      <c r="E47" t="s" s="2">
+        <v>226</v>
+      </c>
       <c r="F47" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>151</v>
+        <v>74</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>74</v>
@@ -6151,10 +6204,12 @@
         <v>74</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>226</v>
+        <v>85</v>
       </c>
       <c r="L47" s="2"/>
-      <c r="M47" s="2"/>
+      <c r="M47" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6204,13 +6259,13 @@
         <v>74</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>74</v>
@@ -6222,18 +6277,20 @@
         <v>74</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E48" s="2"/>
+      <c r="E48" t="s" s="2">
+        <v>230</v>
+      </c>
       <c r="F48" t="s" s="2">
         <v>80</v>
       </c>
@@ -6241,7 +6298,7 @@
         <v>75</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>151</v>
+        <v>74</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>74</v>
@@ -6250,13 +6307,11 @@
         <v>74</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="L48" t="s" s="2">
-        <v>228</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="L48" s="2"/>
       <c r="M48" t="s" s="2">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -6283,11 +6338,11 @@
         <v>74</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>87</v>
+        <v>232</v>
       </c>
       <c r="Y48" s="2"/>
       <c r="Z48" t="s" s="2">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>74</v>
@@ -6305,13 +6360,13 @@
         <v>74</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>74</v>
@@ -6323,12 +6378,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6342,7 +6397,7 @@
         <v>75</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>151</v>
+        <v>74</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>74</v>
@@ -6351,14 +6406,10 @@
         <v>74</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="L49" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>231</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="L49" s="2"/>
+      <c r="M49" s="2"/>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -6388,7 +6439,7 @@
       </c>
       <c r="Y49" s="2"/>
       <c r="Z49" t="s" s="2">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>74</v>
@@ -6406,13 +6457,13 @@
         <v>74</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>74</v>
@@ -6426,10 +6477,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6437,7 +6488,7 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
         <v>75</v>
@@ -6452,15 +6503,17 @@
         <v>74</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>160</v>
+        <v>102</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="N50" s="2"/>
+        <v>240</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>241</v>
+      </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>74</v>
@@ -6509,13 +6562,13 @@
         <v>74</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>74</v>
@@ -6527,28 +6580,28 @@
         <v>74</v>
       </c>
     </row>
-    <row r="51" hidden="true">
+    <row r="51">
       <c r="A51" t="s" s="2">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E51" t="s" s="2">
-        <v>84</v>
+        <v>244</v>
       </c>
       <c r="F51" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G51" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>74</v>
@@ -6557,11 +6610,11 @@
         <v>74</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>85</v>
+        <v>245</v>
       </c>
       <c r="L51" s="2"/>
       <c r="M51" t="s" s="2">
-        <v>86</v>
+        <v>246</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -6588,11 +6641,13 @@
         <v>74</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y51" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z51" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>74</v>
@@ -6610,7 +6665,7 @@
         <v>74</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>89</v>
+        <v>247</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -6630,17 +6685,17 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E52" t="s" s="2">
-        <v>62</v>
+        <v>249</v>
       </c>
       <c r="F52" t="s" s="2">
         <v>80</v>
@@ -6658,11 +6713,11 @@
         <v>74</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>85</v>
+        <v>193</v>
       </c>
       <c r="L52" s="2"/>
       <c r="M52" t="s" s="2">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -6713,7 +6768,7 @@
         <v>74</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -6731,28 +6786,26 @@
         <v>74</v>
       </c>
     </row>
-    <row r="53" hidden="true">
+    <row r="53">
       <c r="A53" t="s" s="2">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E53" t="s" s="2">
-        <v>241</v>
-      </c>
+      <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G53" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>74</v>
@@ -6761,11 +6814,13 @@
         <v>74</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="L53" s="2"/>
+        <v>91</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>253</v>
+      </c>
       <c r="M53" t="s" s="2">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -6792,13 +6847,11 @@
         <v>74</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y53" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y53" s="2"/>
       <c r="Z53" t="s" s="2">
-        <v>74</v>
+        <v>254</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>74</v>
@@ -6816,7 +6869,7 @@
         <v>74</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -6834,20 +6887,18 @@
         <v>74</v>
       </c>
     </row>
-    <row r="54" hidden="true">
+    <row r="54">
       <c r="A54" t="s" s="2">
-        <v>244</v>
+        <v>255</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>244</v>
+        <v>255</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E54" t="s" s="2">
-        <v>245</v>
-      </c>
+      <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>80</v>
       </c>
@@ -6855,7 +6906,7 @@
         <v>75</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>74</v>
@@ -6864,11 +6915,13 @@
         <v>74</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="L54" s="2"/>
+        <v>256</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>257</v>
+      </c>
       <c r="M54" t="s" s="2">
-        <v>246</v>
+        <v>257</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -6919,7 +6972,7 @@
         <v>74</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -6939,18 +6992,16 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E55" t="s" s="2">
-        <v>249</v>
-      </c>
+      <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>80</v>
       </c>
@@ -6967,12 +7018,10 @@
         <v>74</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>102</v>
+        <v>259</v>
       </c>
       <c r="L55" s="2"/>
-      <c r="M55" t="s" s="2">
-        <v>250</v>
-      </c>
+      <c r="M55" s="2"/>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -6998,13 +7047,11 @@
         <v>74</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y55" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="Y55" s="2"/>
       <c r="Z55" t="s" s="2">
-        <v>74</v>
+        <v>260</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>74</v>
@@ -7022,7 +7069,7 @@
         <v>74</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -7042,18 +7089,16 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E56" t="s" s="2">
-        <v>253</v>
-      </c>
+      <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>80</v>
       </c>
@@ -7070,12 +7115,10 @@
         <v>74</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>102</v>
+        <v>262</v>
       </c>
       <c r="L56" s="2"/>
-      <c r="M56" t="s" s="2">
-        <v>254</v>
-      </c>
+      <c r="M56" s="2"/>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -7125,7 +7168,7 @@
         <v>74</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -7145,10 +7188,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7171,12 +7214,10 @@
         <v>74</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>257</v>
+        <v>91</v>
       </c>
       <c r="L57" s="2"/>
-      <c r="M57" t="s" s="2">
-        <v>258</v>
-      </c>
+      <c r="M57" s="2"/>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -7202,13 +7243,11 @@
         <v>74</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y57" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y57" s="2"/>
       <c r="Z57" t="s" s="2">
-        <v>74</v>
+        <v>264</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>74</v>
@@ -7226,7 +7265,7 @@
         <v>74</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -7244,12 +7283,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="58" hidden="true">
+    <row r="58">
       <c r="A58" t="s" s="2">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7257,13 +7296,13 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G58" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>74</v>
@@ -7272,12 +7311,10 @@
         <v>74</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>102</v>
+        <v>266</v>
       </c>
       <c r="L58" s="2"/>
-      <c r="M58" t="s" s="2">
-        <v>261</v>
-      </c>
+      <c r="M58" s="2"/>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -7327,13 +7364,13 @@
         <v>74</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>74</v>
@@ -7345,20 +7382,18 @@
         <v>74</v>
       </c>
     </row>
-    <row r="59" hidden="true">
+    <row r="59">
       <c r="A59" t="s" s="2">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E59" t="s" s="2">
-        <v>264</v>
-      </c>
+      <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>80</v>
       </c>
@@ -7366,7 +7401,7 @@
         <v>75</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>74</v>
@@ -7375,11 +7410,13 @@
         <v>74</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="L59" s="2"/>
+        <v>259</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>268</v>
+      </c>
       <c r="M59" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -7406,13 +7443,11 @@
         <v>74</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y59" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y59" s="2"/>
       <c r="Z59" t="s" s="2">
-        <v>74</v>
+        <v>269</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>74</v>
@@ -7430,13 +7465,13 @@
         <v>74</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>74</v>
@@ -7450,18 +7485,16 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E60" t="s" s="2">
-        <v>268</v>
-      </c>
+      <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
         <v>80</v>
       </c>
@@ -7478,13 +7511,13 @@
         <v>74</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -7511,13 +7544,11 @@
         <v>74</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y60" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y60" s="2"/>
       <c r="Z60" t="s" s="2">
-        <v>74</v>
+        <v>272</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>74</v>
@@ -7535,7 +7566,7 @@
         <v>74</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -7555,20 +7586,18 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E61" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G61" t="s" s="2">
         <v>75</v>
@@ -7583,11 +7612,13 @@
         <v>74</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="L61" s="2"/>
+        <v>160</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>274</v>
+      </c>
       <c r="M61" t="s" s="2">
-        <v>86</v>
+        <v>275</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -7614,11 +7645,13 @@
         <v>74</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y61" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z61" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>74</v>
@@ -7636,13 +7669,13 @@
         <v>74</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>89</v>
+        <v>273</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>74</v>
@@ -7656,17 +7689,17 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E62" t="s" s="2">
-        <v>274</v>
+        <v>84</v>
       </c>
       <c r="F62" t="s" s="2">
         <v>80</v>
@@ -7684,11 +7717,11 @@
         <v>74</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>275</v>
+        <v>85</v>
       </c>
       <c r="L62" s="2"/>
       <c r="M62" t="s" s="2">
-        <v>276</v>
+        <v>86</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -7715,13 +7748,11 @@
         <v>74</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y62" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y62" s="2"/>
       <c r="Z62" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>74</v>
@@ -7739,46 +7770,46 @@
         <v>74</v>
       </c>
       <c r="AF62" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="63" hidden="true">
+      <c r="A63" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="AG62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH62" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI62" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ62" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK62" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="s" s="2">
-        <v>278</v>
-      </c>
       <c r="B63" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E63" t="s" s="2">
-        <v>6</v>
+        <v>62</v>
       </c>
       <c r="F63" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G63" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>151</v>
+        <v>74</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>74</v>
@@ -7787,11 +7818,11 @@
         <v>74</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>279</v>
+        <v>85</v>
       </c>
       <c r="L63" s="2"/>
       <c r="M63" t="s" s="2">
-        <v>280</v>
+        <v>166</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -7842,7 +7873,7 @@
         <v>74</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>281</v>
+        <v>167</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -7862,17 +7893,17 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E64" t="s" s="2">
-        <v>84</v>
+        <v>169</v>
       </c>
       <c r="F64" t="s" s="2">
         <v>80</v>
@@ -7890,11 +7921,11 @@
         <v>74</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>85</v>
+        <v>112</v>
       </c>
       <c r="L64" s="2"/>
       <c r="M64" t="s" s="2">
-        <v>86</v>
+        <v>170</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -7921,11 +7952,13 @@
         <v>74</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y64" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z64" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>74</v>
@@ -7943,7 +7976,7 @@
         <v>74</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>89</v>
+        <v>171</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -7963,17 +7996,17 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E65" t="s" s="2">
-        <v>62</v>
+        <v>173</v>
       </c>
       <c r="F65" t="s" s="2">
         <v>80</v>
@@ -7991,11 +8024,11 @@
         <v>74</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="L65" s="2"/>
       <c r="M65" t="s" s="2">
-        <v>238</v>
+        <v>174</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -8007,7 +8040,7 @@
         <v>74</v>
       </c>
       <c r="S65" t="s" s="2">
-        <v>284</v>
+        <v>74</v>
       </c>
       <c r="T65" t="s" s="2">
         <v>74</v>
@@ -8046,7 +8079,7 @@
         <v>74</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>239</v>
+        <v>175</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -8066,17 +8099,17 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E66" t="s" s="2">
-        <v>241</v>
+        <v>177</v>
       </c>
       <c r="F66" t="s" s="2">
         <v>80</v>
@@ -8094,11 +8127,11 @@
         <v>74</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="L66" s="2"/>
       <c r="M66" t="s" s="2">
-        <v>242</v>
+        <v>178</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -8110,7 +8143,7 @@
         <v>74</v>
       </c>
       <c r="S66" t="s" s="2">
-        <v>286</v>
+        <v>74</v>
       </c>
       <c r="T66" t="s" s="2">
         <v>74</v>
@@ -8149,7 +8182,7 @@
         <v>74</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>243</v>
+        <v>179</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -8169,17 +8202,17 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E67" t="s" s="2">
-        <v>245</v>
+        <v>181</v>
       </c>
       <c r="F67" t="s" s="2">
         <v>80</v>
@@ -8201,7 +8234,7 @@
       </c>
       <c r="L67" s="2"/>
       <c r="M67" t="s" s="2">
-        <v>246</v>
+        <v>182</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -8213,7 +8246,7 @@
         <v>74</v>
       </c>
       <c r="S67" t="s" s="2">
-        <v>288</v>
+        <v>74</v>
       </c>
       <c r="T67" t="s" s="2">
         <v>74</v>
@@ -8252,7 +8285,7 @@
         <v>74</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>247</v>
+        <v>183</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -8272,18 +8305,16 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E68" t="s" s="2">
-        <v>249</v>
-      </c>
+      <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
         <v>80</v>
       </c>
@@ -8300,11 +8331,11 @@
         <v>74</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>102</v>
+        <v>185</v>
       </c>
       <c r="L68" s="2"/>
       <c r="M68" t="s" s="2">
-        <v>250</v>
+        <v>186</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -8355,7 +8386,7 @@
         <v>74</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>251</v>
+        <v>187</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -8375,18 +8406,16 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E69" t="s" s="2">
-        <v>253</v>
-      </c>
+      <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
         <v>80</v>
       </c>
@@ -8407,7 +8436,7 @@
       </c>
       <c r="L69" s="2"/>
       <c r="M69" t="s" s="2">
-        <v>254</v>
+        <v>189</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -8419,7 +8448,7 @@
         <v>74</v>
       </c>
       <c r="S69" t="s" s="2">
-        <v>291</v>
+        <v>74</v>
       </c>
       <c r="T69" t="s" s="2">
         <v>74</v>
@@ -8458,7 +8487,7 @@
         <v>74</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>255</v>
+        <v>190</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -8478,16 +8507,18 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E70" s="2"/>
+      <c r="E70" t="s" s="2">
+        <v>192</v>
+      </c>
       <c r="F70" t="s" s="2">
         <v>80</v>
       </c>
@@ -8504,11 +8535,11 @@
         <v>74</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>257</v>
+        <v>193</v>
       </c>
       <c r="L70" s="2"/>
       <c r="M70" t="s" s="2">
-        <v>258</v>
+        <v>194</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -8559,7 +8590,7 @@
         <v>74</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>259</v>
+        <v>195</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -8577,18 +8608,20 @@
         <v>74</v>
       </c>
     </row>
-    <row r="71" hidden="true">
+    <row r="71">
       <c r="A71" t="s" s="2">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E71" s="2"/>
+      <c r="E71" t="s" s="2">
+        <v>197</v>
+      </c>
       <c r="F71" t="s" s="2">
         <v>80</v>
       </c>
@@ -8596,7 +8629,7 @@
         <v>75</v>
       </c>
       <c r="H71" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I71" t="s" s="2">
         <v>74</v>
@@ -8605,11 +8638,13 @@
         <v>74</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="L71" s="2"/>
+        <v>198</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>286</v>
+      </c>
       <c r="M71" t="s" s="2">
-        <v>261</v>
+        <v>286</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -8660,13 +8695,13 @@
         <v>74</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>262</v>
+        <v>200</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>74</v>
@@ -8680,17 +8715,17 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E72" t="s" s="2">
-        <v>264</v>
+        <v>84</v>
       </c>
       <c r="F72" t="s" s="2">
         <v>80</v>
@@ -8708,11 +8743,11 @@
         <v>74</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>167</v>
+        <v>85</v>
       </c>
       <c r="L72" s="2"/>
       <c r="M72" t="s" s="2">
-        <v>265</v>
+        <v>86</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -8739,13 +8774,11 @@
         <v>74</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y72" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y72" s="2"/>
       <c r="Z72" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>74</v>
@@ -8763,7 +8796,7 @@
         <v>74</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>266</v>
+        <v>89</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -8783,23 +8816,23 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E73" t="s" s="2">
-        <v>268</v>
+        <v>289</v>
       </c>
       <c r="F73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>74</v>
@@ -8811,11 +8844,11 @@
         <v>74</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>269</v>
+        <v>290</v>
       </c>
       <c r="L73" s="2"/>
       <c r="M73" t="s" s="2">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -8866,13 +8899,13 @@
         <v>74</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>74</v>
@@ -8884,28 +8917,28 @@
         <v>74</v>
       </c>
     </row>
-    <row r="74" hidden="true">
+    <row r="74">
       <c r="A74" t="s" s="2">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E74" t="s" s="2">
-        <v>298</v>
+        <v>6</v>
       </c>
       <c r="F74" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H74" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I74" t="s" s="2">
         <v>74</v>
@@ -8914,11 +8947,11 @@
         <v>74</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>160</v>
+        <v>294</v>
       </c>
       <c r="L74" s="2"/>
       <c r="M74" t="s" s="2">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -8969,13 +9002,13 @@
         <v>74</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>74</v>
@@ -8987,28 +9020,28 @@
         <v>74</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E75" t="s" s="2">
-        <v>1</v>
+        <v>84</v>
       </c>
       <c r="F75" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G75" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H75" t="s" s="2">
-        <v>151</v>
+        <v>74</v>
       </c>
       <c r="I75" t="s" s="2">
         <v>74</v>
@@ -9017,13 +9050,11 @@
         <v>74</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="L75" t="s" s="2">
-        <v>302</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="L75" s="2"/>
       <c r="M75" t="s" s="2">
-        <v>302</v>
+        <v>86</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -9054,7 +9085,7 @@
       </c>
       <c r="Y75" s="2"/>
       <c r="Z75" t="s" s="2">
-        <v>303</v>
+        <v>88</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>74</v>
@@ -9072,7 +9103,7 @@
         <v>74</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>304</v>
+        <v>89</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -9092,23 +9123,23 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E76" t="s" s="2">
-        <v>298</v>
+        <v>62</v>
       </c>
       <c r="F76" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>74</v>
@@ -9120,11 +9151,11 @@
         <v>74</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>160</v>
+        <v>85</v>
       </c>
       <c r="L76" s="2"/>
       <c r="M76" t="s" s="2">
-        <v>299</v>
+        <v>166</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -9136,7 +9167,7 @@
         <v>74</v>
       </c>
       <c r="S76" t="s" s="2">
-        <v>74</v>
+        <v>299</v>
       </c>
       <c r="T76" t="s" s="2">
         <v>74</v>
@@ -9175,13 +9206,13 @@
         <v>74</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>300</v>
+        <v>167</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>74</v>
@@ -9195,16 +9226,18 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E77" s="2"/>
+      <c r="E77" t="s" s="2">
+        <v>169</v>
+      </c>
       <c r="F77" t="s" s="2">
         <v>80</v>
       </c>
@@ -9221,10 +9254,12 @@
         <v>74</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>307</v>
+        <v>112</v>
       </c>
       <c r="L77" s="2"/>
-      <c r="M77" s="2"/>
+      <c r="M77" t="s" s="2">
+        <v>170</v>
+      </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -9235,7 +9270,7 @@
         <v>74</v>
       </c>
       <c r="S77" t="s" s="2">
-        <v>74</v>
+        <v>301</v>
       </c>
       <c r="T77" t="s" s="2">
         <v>74</v>
@@ -9274,7 +9309,7 @@
         <v>74</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>306</v>
+        <v>171</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -9294,21 +9329,23 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E78" s="2"/>
+      <c r="E78" t="s" s="2">
+        <v>173</v>
+      </c>
       <c r="F78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>74</v>
@@ -9320,10 +9357,12 @@
         <v>74</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>309</v>
+        <v>102</v>
       </c>
       <c r="L78" s="2"/>
-      <c r="M78" s="2"/>
+      <c r="M78" t="s" s="2">
+        <v>174</v>
+      </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -9334,7 +9373,7 @@
         <v>74</v>
       </c>
       <c r="S78" t="s" s="2">
-        <v>74</v>
+        <v>303</v>
       </c>
       <c r="T78" t="s" s="2">
         <v>74</v>
@@ -9373,13 +9412,13 @@
         <v>74</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>308</v>
+        <v>175</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>74</v>
@@ -9393,21 +9432,23 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E79" s="2"/>
+      <c r="E79" t="s" s="2">
+        <v>177</v>
+      </c>
       <c r="F79" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>74</v>
@@ -9419,10 +9460,12 @@
         <v>74</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>311</v>
+        <v>102</v>
       </c>
       <c r="L79" s="2"/>
-      <c r="M79" s="2"/>
+      <c r="M79" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -9472,13 +9515,13 @@
         <v>74</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>310</v>
+        <v>179</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>74</v>
@@ -9492,21 +9535,23 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E80" s="2"/>
+      <c r="E80" t="s" s="2">
+        <v>181</v>
+      </c>
       <c r="F80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>74</v>
@@ -9518,10 +9563,12 @@
         <v>74</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>313</v>
+        <v>102</v>
       </c>
       <c r="L80" s="2"/>
-      <c r="M80" s="2"/>
+      <c r="M80" t="s" s="2">
+        <v>182</v>
+      </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -9532,7 +9579,7 @@
         <v>74</v>
       </c>
       <c r="S80" t="s" s="2">
-        <v>74</v>
+        <v>306</v>
       </c>
       <c r="T80" t="s" s="2">
         <v>74</v>
@@ -9571,13 +9618,13 @@
         <v>74</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>312</v>
+        <v>183</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>74</v>
@@ -9591,10 +9638,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -9605,7 +9652,7 @@
         <v>80</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>74</v>
@@ -9617,10 +9664,12 @@
         <v>74</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>315</v>
+        <v>185</v>
       </c>
       <c r="L81" s="2"/>
-      <c r="M81" s="2"/>
+      <c r="M81" t="s" s="2">
+        <v>186</v>
+      </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -9670,13 +9719,13 @@
         <v>74</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>314</v>
+        <v>187</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>74</v>
@@ -9690,10 +9739,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -9704,7 +9753,7 @@
         <v>80</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>74</v>
@@ -9716,10 +9765,12 @@
         <v>74</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>317</v>
+        <v>102</v>
       </c>
       <c r="L82" s="2"/>
-      <c r="M82" s="2"/>
+      <c r="M82" t="s" s="2">
+        <v>189</v>
+      </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -9769,13 +9820,13 @@
         <v>74</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>316</v>
+        <v>190</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>74</v>
@@ -9789,21 +9840,23 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E83" s="2"/>
+      <c r="E83" t="s" s="2">
+        <v>192</v>
+      </c>
       <c r="F83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>74</v>
@@ -9815,10 +9868,12 @@
         <v>74</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>319</v>
+        <v>193</v>
       </c>
       <c r="L83" s="2"/>
-      <c r="M83" s="2"/>
+      <c r="M83" t="s" s="2">
+        <v>194</v>
+      </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -9868,13 +9923,13 @@
         <v>74</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>318</v>
+        <v>195</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>74</v>
@@ -9888,21 +9943,23 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E84" s="2"/>
+      <c r="E84" t="s" s="2">
+        <v>197</v>
+      </c>
       <c r="F84" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>74</v>
@@ -9914,10 +9971,12 @@
         <v>74</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>321</v>
+        <v>198</v>
       </c>
       <c r="L84" s="2"/>
-      <c r="M84" s="2"/>
+      <c r="M84" t="s" s="2">
+        <v>199</v>
+      </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -9967,7 +10026,7 @@
         <v>74</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>320</v>
+        <v>200</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -9987,21 +10046,23 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>322</v>
+        <v>311</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>322</v>
+        <v>311</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E85" s="2"/>
+      <c r="E85" t="s" s="2">
+        <v>202</v>
+      </c>
       <c r="F85" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>74</v>
@@ -10013,10 +10074,12 @@
         <v>74</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>323</v>
+        <v>160</v>
       </c>
       <c r="L85" s="2"/>
-      <c r="M85" s="2"/>
+      <c r="M85" t="s" s="2">
+        <v>203</v>
+      </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -10066,7 +10129,7 @@
         <v>74</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>322</v>
+        <v>204</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -10084,26 +10147,28 @@
         <v>74</v>
       </c>
     </row>
-    <row r="86" hidden="true">
+    <row r="86">
       <c r="A86" t="s" s="2">
-        <v>324</v>
+        <v>312</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>324</v>
+        <v>312</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E86" s="2"/>
+      <c r="E86" t="s" s="2">
+        <v>1</v>
+      </c>
       <c r="F86" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H86" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I86" t="s" s="2">
         <v>74</v>
@@ -10112,10 +10177,14 @@
         <v>74</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="L86" s="2"/>
-      <c r="M86" s="2"/>
+        <v>160</v>
+      </c>
+      <c r="L86" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="M86" t="s" s="2">
+        <v>313</v>
+      </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -10141,13 +10210,11 @@
         <v>74</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y86" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y86" s="2"/>
       <c r="Z86" t="s" s="2">
-        <v>74</v>
+        <v>314</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>74</v>
@@ -10165,13 +10232,13 @@
         <v>74</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>74</v>
@@ -10185,16 +10252,18 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E87" s="2"/>
+      <c r="E87" t="s" s="2">
+        <v>202</v>
+      </c>
       <c r="F87" t="s" s="2">
         <v>80</v>
       </c>
@@ -10211,11 +10280,11 @@
         <v>74</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>327</v>
+        <v>160</v>
       </c>
       <c r="L87" s="2"/>
       <c r="M87" t="s" s="2">
-        <v>328</v>
+        <v>203</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -10266,7 +10335,7 @@
         <v>74</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>326</v>
+        <v>204</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -10286,18 +10355,16 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>329</v>
+        <v>317</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>329</v>
+        <v>317</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E88" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
         <v>80</v>
       </c>
@@ -10314,12 +10381,10 @@
         <v>74</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>85</v>
+        <v>318</v>
       </c>
       <c r="L88" s="2"/>
-      <c r="M88" t="s" s="2">
-        <v>86</v>
-      </c>
+      <c r="M88" s="2"/>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -10345,11 +10410,13 @@
         <v>74</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y88" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y88" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z88" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>74</v>
@@ -10367,7 +10434,7 @@
         <v>74</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>89</v>
+        <v>317</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -10387,10 +10454,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>330</v>
+        <v>319</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>330</v>
+        <v>319</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -10413,12 +10480,10 @@
         <v>74</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>91</v>
+        <v>320</v>
       </c>
       <c r="L89" s="2"/>
-      <c r="M89" t="s" s="2">
-        <v>92</v>
-      </c>
+      <c r="M89" s="2"/>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -10468,7 +10533,7 @@
         <v>74</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>93</v>
+        <v>319</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -10488,10 +10553,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -10502,7 +10567,7 @@
         <v>80</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>74</v>
@@ -10514,12 +10579,10 @@
         <v>74</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>95</v>
+        <v>322</v>
       </c>
       <c r="L90" s="2"/>
-      <c r="M90" t="s" s="2">
-        <v>96</v>
-      </c>
+      <c r="M90" s="2"/>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -10569,19 +10632,19 @@
         <v>74</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>97</v>
+        <v>321</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI90" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>74</v>
@@ -10589,23 +10652,21 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E91" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>74</v>
@@ -10617,12 +10678,10 @@
         <v>74</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>85</v>
+        <v>324</v>
       </c>
       <c r="L91" s="2"/>
-      <c r="M91" t="s" s="2">
-        <v>86</v>
-      </c>
+      <c r="M91" s="2"/>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -10648,11 +10707,13 @@
         <v>74</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y91" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y91" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z91" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>74</v>
@@ -10670,13 +10731,13 @@
         <v>74</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>89</v>
+        <v>323</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI91" t="s" s="2">
         <v>74</v>
@@ -10690,23 +10751,21 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E92" t="s" s="2">
-        <v>101</v>
-      </c>
+      <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>74</v>
@@ -10718,12 +10777,10 @@
         <v>74</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>102</v>
+        <v>326</v>
       </c>
       <c r="L92" s="2"/>
-      <c r="M92" t="s" s="2">
-        <v>103</v>
-      </c>
+      <c r="M92" s="2"/>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -10773,13 +10830,13 @@
         <v>74</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>104</v>
+        <v>325</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>74</v>
@@ -10793,23 +10850,21 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E93" t="s" s="2">
-        <v>106</v>
-      </c>
+      <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>74</v>
@@ -10821,12 +10876,10 @@
         <v>74</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>107</v>
+        <v>328</v>
       </c>
       <c r="L93" s="2"/>
-      <c r="M93" t="s" s="2">
-        <v>108</v>
-      </c>
+      <c r="M93" s="2"/>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -10876,13 +10929,13 @@
         <v>74</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>109</v>
+        <v>327</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>74</v>
@@ -10896,23 +10949,21 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E94" t="s" s="2">
-        <v>111</v>
-      </c>
+      <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>74</v>
@@ -10924,12 +10975,10 @@
         <v>74</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>112</v>
+        <v>330</v>
       </c>
       <c r="L94" s="2"/>
-      <c r="M94" t="s" s="2">
-        <v>113</v>
-      </c>
+      <c r="M94" s="2"/>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -10937,7 +10986,7 @@
       </c>
       <c r="Q94" s="2"/>
       <c r="R94" t="s" s="2">
-        <v>114</v>
+        <v>74</v>
       </c>
       <c r="S94" t="s" s="2">
         <v>74</v>
@@ -10979,13 +11028,13 @@
         <v>74</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>115</v>
+        <v>329</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI94" t="s" s="2">
         <v>74</v>
@@ -10999,23 +11048,21 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E95" t="s" s="2">
-        <v>117</v>
-      </c>
+      <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>74</v>
@@ -11027,12 +11074,10 @@
         <v>74</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>102</v>
+        <v>332</v>
       </c>
       <c r="L95" s="2"/>
-      <c r="M95" t="s" s="2">
-        <v>118</v>
-      </c>
+      <c r="M95" s="2"/>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -11082,13 +11127,13 @@
         <v>74</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>119</v>
+        <v>331</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI95" t="s" s="2">
         <v>74</v>
@@ -11102,10 +11147,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -11128,12 +11173,10 @@
         <v>74</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>95</v>
+        <v>334</v>
       </c>
       <c r="L96" s="2"/>
-      <c r="M96" t="s" s="2">
-        <v>122</v>
-      </c>
+      <c r="M96" s="2"/>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -11183,7 +11226,7 @@
         <v>74</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>125</v>
+        <v>333</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -11203,10 +11246,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -11217,7 +11260,7 @@
         <v>80</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H97" t="s" s="2">
         <v>74</v>
@@ -11229,7 +11272,7 @@
         <v>74</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>85</v>
+        <v>336</v>
       </c>
       <c r="L97" s="2"/>
       <c r="M97" s="2"/>
@@ -11240,7 +11283,7 @@
       </c>
       <c r="Q97" s="2"/>
       <c r="R97" t="s" s="2">
-        <v>339</v>
+        <v>74</v>
       </c>
       <c r="S97" t="s" s="2">
         <v>74</v>
@@ -11258,11 +11301,13 @@
         <v>74</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y97" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y97" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z97" t="s" s="2">
-        <v>340</v>
+        <v>74</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>74</v>
@@ -11280,13 +11325,13 @@
         <v>74</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI97" t="s" s="2">
         <v>74</v>
@@ -11300,10 +11345,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -11311,10 +11356,10 @@
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H98" t="s" s="2">
         <v>74</v>
@@ -11326,10 +11371,12 @@
         <v>74</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="L98" s="2"/>
-      <c r="M98" s="2"/>
+      <c r="M98" t="s" s="2">
+        <v>339</v>
+      </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -11379,13 +11426,13 @@
         <v>74</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="AG98" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AH98" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI98" t="s" s="2">
         <v>74</v>
@@ -11399,21 +11446,23 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E99" s="2"/>
+      <c r="E99" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F99" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H99" t="s" s="2">
         <v>74</v>
@@ -11425,10 +11474,12 @@
         <v>74</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>344</v>
+        <v>85</v>
       </c>
       <c r="L99" s="2"/>
-      <c r="M99" s="2"/>
+      <c r="M99" t="s" s="2">
+        <v>86</v>
+      </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -11454,13 +11505,11 @@
         <v>74</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y99" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y99" s="2"/>
       <c r="Z99" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>74</v>
@@ -11478,26 +11527,1137 @@
         <v>74</v>
       </c>
       <c r="AF99" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AG99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH99" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI99" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ99" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK99" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="100" hidden="true">
+      <c r="A100" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="B100" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="C100" s="2"/>
+      <c r="D100" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E100" s="2"/>
+      <c r="F100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H100" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I100" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J100" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K100" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="L100" s="2"/>
+      <c r="M100" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="N100" s="2"/>
+      <c r="O100" s="2"/>
+      <c r="P100" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q100" s="2"/>
+      <c r="R100" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S100" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T100" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U100" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V100" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W100" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X100" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y100" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z100" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA100" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB100" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC100" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD100" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE100" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF100" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AG100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI100" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ100" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK100" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="101" hidden="true">
+      <c r="A101" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="B101" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="C101" s="2"/>
+      <c r="D101" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E101" s="2"/>
+      <c r="F101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G101" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H101" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I101" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J101" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K101" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="L101" s="2"/>
+      <c r="M101" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="N101" s="2"/>
+      <c r="O101" s="2"/>
+      <c r="P101" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q101" s="2"/>
+      <c r="R101" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S101" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T101" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U101" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V101" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W101" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X101" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y101" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z101" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA101" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB101" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC101" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD101" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE101" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF101" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AG101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH101" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI101" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ101" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK101" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="102" hidden="true">
+      <c r="A102" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="AG99" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH99" t="s" s="2">
+      <c r="B102" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="C102" s="2"/>
+      <c r="D102" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E102" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="F102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G102" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H102" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I102" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J102" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K102" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L102" s="2"/>
+      <c r="M102" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="N102" s="2"/>
+      <c r="O102" s="2"/>
+      <c r="P102" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q102" s="2"/>
+      <c r="R102" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S102" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T102" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U102" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V102" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W102" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X102" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="Y102" s="2"/>
+      <c r="Z102" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AA102" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB102" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC102" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD102" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE102" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF102" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AG102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH102" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI102" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ102" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK102" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="103" hidden="true">
+      <c r="A103" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="B103" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="C103" s="2"/>
+      <c r="D103" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E103" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="F103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G103" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H103" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I103" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J103" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K103" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L103" s="2"/>
+      <c r="M103" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="N103" s="2"/>
+      <c r="O103" s="2"/>
+      <c r="P103" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q103" s="2"/>
+      <c r="R103" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S103" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T103" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U103" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V103" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W103" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X103" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y103" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z103" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA103" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB103" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC103" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD103" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE103" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF103" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AG103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH103" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI103" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ103" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK103" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="104" hidden="true">
+      <c r="A104" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="B104" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="C104" s="2"/>
+      <c r="D104" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E104" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="F104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G104" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H104" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I104" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J104" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K104" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L104" s="2"/>
+      <c r="M104" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="N104" s="2"/>
+      <c r="O104" s="2"/>
+      <c r="P104" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q104" s="2"/>
+      <c r="R104" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S104" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T104" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U104" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V104" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W104" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X104" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y104" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z104" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA104" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB104" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC104" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD104" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE104" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF104" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AG104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH104" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI104" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ104" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK104" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="105" hidden="true">
+      <c r="A105" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="B105" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="C105" s="2"/>
+      <c r="D105" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E105" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="F105" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G105" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H105" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I105" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J105" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K105" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L105" s="2"/>
+      <c r="M105" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="N105" s="2"/>
+      <c r="O105" s="2"/>
+      <c r="P105" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q105" s="2"/>
+      <c r="R105" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="S105" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T105" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U105" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V105" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W105" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X105" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y105" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z105" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA105" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB105" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC105" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD105" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE105" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF105" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AG105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH105" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI105" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ105" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK105" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="106" hidden="true">
+      <c r="A106" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="B106" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="C106" s="2"/>
+      <c r="D106" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E106" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="F106" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G106" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H106" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I106" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J106" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K106" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L106" s="2"/>
+      <c r="M106" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="N106" s="2"/>
+      <c r="O106" s="2"/>
+      <c r="P106" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q106" s="2"/>
+      <c r="R106" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S106" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T106" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U106" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V106" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W106" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X106" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y106" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z106" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA106" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB106" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC106" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD106" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE106" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF106" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AG106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH106" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI106" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ106" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK106" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="107" hidden="true">
+      <c r="A107" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="B107" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="C107" s="2"/>
+      <c r="D107" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E107" s="2"/>
+      <c r="F107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G107" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="AI99" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ99" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK99" t="s" s="2">
+      <c r="H107" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I107" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J107" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K107" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="L107" s="2"/>
+      <c r="M107" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="N107" s="2"/>
+      <c r="O107" s="2"/>
+      <c r="P107" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q107" s="2"/>
+      <c r="R107" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S107" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T107" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U107" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V107" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W107" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X107" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y107" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z107" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA107" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB107" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC107" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD107" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE107" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF107" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="AG107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI107" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ107" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK107" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="108" hidden="true">
+      <c r="A108" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="B108" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="C108" s="2"/>
+      <c r="D108" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E108" s="2"/>
+      <c r="F108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G108" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H108" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I108" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J108" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K108" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L108" s="2"/>
+      <c r="M108" s="2"/>
+      <c r="N108" s="2"/>
+      <c r="O108" s="2"/>
+      <c r="P108" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q108" s="2"/>
+      <c r="R108" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="S108" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T108" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U108" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V108" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W108" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X108" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="Y108" s="2"/>
+      <c r="Z108" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="AA108" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB108" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC108" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD108" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE108" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF108" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="AG108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH108" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI108" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ108" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK108" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="109" hidden="true">
+      <c r="A109" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="B109" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="C109" s="2"/>
+      <c r="D109" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E109" s="2"/>
+      <c r="F109" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G109" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H109" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I109" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J109" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K109" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="L109" s="2"/>
+      <c r="M109" s="2"/>
+      <c r="N109" s="2"/>
+      <c r="O109" s="2"/>
+      <c r="P109" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q109" s="2"/>
+      <c r="R109" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S109" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T109" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U109" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V109" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W109" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X109" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y109" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z109" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA109" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB109" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC109" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD109" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE109" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF109" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="AG109" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH109" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI109" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ109" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK109" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="110" hidden="true">
+      <c r="A110" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="B110" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="C110" s="2"/>
+      <c r="D110" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E110" s="2"/>
+      <c r="F110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G110" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H110" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I110" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J110" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K110" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="L110" s="2"/>
+      <c r="M110" s="2"/>
+      <c r="N110" s="2"/>
+      <c r="O110" s="2"/>
+      <c r="P110" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q110" s="2"/>
+      <c r="R110" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S110" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T110" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U110" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V110" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W110" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X110" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y110" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z110" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA110" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB110" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC110" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD110" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE110" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF110" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="AG110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH110" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI110" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ110" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK110" t="s" s="2">
         <v>74</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AK99">
+  <autoFilter ref="A1:AK110">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -11507,7 +12667,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI98">
+  <conditionalFormatting sqref="A2:AI109">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/main/ig/StructureDefinition-fr-cda-dicom-quantite-subordonnee.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-dicom-quantite-subordonnee.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T15:11:12+00:00</t>
+    <t>2026-04-23T15:25:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-dicom-quantite-subordonnee.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-dicom-quantite-subordonnee.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T15:25:59+00:00</t>
+    <t>2026-05-06T07:44:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-dicom-quantite-subordonnee.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-dicom-quantite-subordonnee.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T07:44:21+00:00</t>
+    <t>2026-05-13T14:53:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-dicom-quantite-subordonnee.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-dicom-quantite-subordonnee.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T14:53:03+00:00</t>
+    <t>2026-05-15T08:08:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-dicom-quantite-subordonnee.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-dicom-quantite-subordonnee.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T09:35:10+00:00</t>
+    <t>2026-06-29T12:53:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-dicom-quantite-subordonnee.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-dicom-quantite-subordonnee.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3482" uniqueCount="356">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3482" uniqueCount="357">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:53:00+00:00</t>
+    <t>2026-06-29T14:20:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -788,6 +788,10 @@
   </si>
   <si>
     <t>ED.thumbnail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ED-1:Thumbnails cannot contain their own thumbnails {thumbnail.empty()}
+</t>
   </si>
   <si>
     <t>Observation.statusCode</t>
@@ -6780,7 +6784,7 @@
         <v>74</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>74</v>
+        <v>252</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>74</v>
@@ -6788,10 +6792,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6817,10 +6821,10 @@
         <v>91</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -6851,7 +6855,7 @@
       </c>
       <c r="Y53" s="2"/>
       <c r="Z53" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>74</v>
@@ -6869,7 +6873,7 @@
         <v>74</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -6889,10 +6893,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -6915,13 +6919,13 @@
         <v>74</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -6972,7 +6976,7 @@
         <v>74</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -6992,10 +6996,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7018,7 +7022,7 @@
         <v>74</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L55" s="2"/>
       <c r="M55" s="2"/>
@@ -7051,7 +7055,7 @@
       </c>
       <c r="Y55" s="2"/>
       <c r="Z55" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>74</v>
@@ -7069,7 +7073,7 @@
         <v>74</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -7089,10 +7093,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7115,7 +7119,7 @@
         <v>74</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L56" s="2"/>
       <c r="M56" s="2"/>
@@ -7168,7 +7172,7 @@
         <v>74</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -7188,10 +7192,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7247,25 +7251,25 @@
       </c>
       <c r="Y57" s="2"/>
       <c r="Z57" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF57" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="AA57" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB57" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC57" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD57" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE57" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF57" t="s" s="2">
-        <v>263</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -7285,10 +7289,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7311,7 +7315,7 @@
         <v>74</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="L58" s="2"/>
       <c r="M58" s="2"/>
@@ -7364,7 +7368,7 @@
         <v>74</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -7384,10 +7388,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7410,13 +7414,13 @@
         <v>74</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -7447,7 +7451,7 @@
       </c>
       <c r="Y59" s="2"/>
       <c r="Z59" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>74</v>
@@ -7465,7 +7469,7 @@
         <v>74</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -7485,10 +7489,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7511,13 +7515,13 @@
         <v>74</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -7548,7 +7552,7 @@
       </c>
       <c r="Y60" s="2"/>
       <c r="Z60" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>74</v>
@@ -7566,7 +7570,7 @@
         <v>74</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -7586,10 +7590,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7615,10 +7619,10 @@
         <v>160</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -7669,7 +7673,7 @@
         <v>74</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -7689,10 +7693,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -7790,10 +7794,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -7893,10 +7897,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -7996,10 +8000,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8099,10 +8103,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8202,10 +8206,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8305,10 +8309,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8406,10 +8410,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -8507,10 +8511,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -8610,10 +8614,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -8641,10 +8645,10 @@
         <v>198</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -8715,10 +8719,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -8816,17 +8820,17 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E73" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F73" t="s" s="2">
         <v>80</v>
@@ -8844,11 +8848,11 @@
         <v>74</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="L73" s="2"/>
       <c r="M73" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -8899,7 +8903,7 @@
         <v>74</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -8919,10 +8923,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -8947,11 +8951,11 @@
         <v>74</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="L74" s="2"/>
       <c r="M74" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -9002,7 +9006,7 @@
         <v>74</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -9022,10 +9026,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -9123,10 +9127,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9167,7 +9171,7 @@
         <v>74</v>
       </c>
       <c r="S76" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="T76" t="s" s="2">
         <v>74</v>
@@ -9226,10 +9230,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9270,7 +9274,7 @@
         <v>74</v>
       </c>
       <c r="S77" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="T77" t="s" s="2">
         <v>74</v>
@@ -9329,10 +9333,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9373,7 +9377,7 @@
         <v>74</v>
       </c>
       <c r="S78" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="T78" t="s" s="2">
         <v>74</v>
@@ -9432,10 +9436,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -9535,10 +9539,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -9579,7 +9583,7 @@
         <v>74</v>
       </c>
       <c r="S80" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="T80" t="s" s="2">
         <v>74</v>
@@ -9638,10 +9642,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -9739,10 +9743,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -9840,10 +9844,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -9943,10 +9947,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -10046,10 +10050,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10149,10 +10153,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -10180,10 +10184,10 @@
         <v>160</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -10214,7 +10218,7 @@
       </c>
       <c r="Y86" s="2"/>
       <c r="Z86" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>74</v>
@@ -10232,7 +10236,7 @@
         <v>74</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -10252,10 +10256,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -10355,10 +10359,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -10381,7 +10385,7 @@
         <v>74</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L88" s="2"/>
       <c r="M88" s="2"/>
@@ -10434,7 +10438,7 @@
         <v>74</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -10454,10 +10458,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -10480,7 +10484,7 @@
         <v>74</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="L89" s="2"/>
       <c r="M89" s="2"/>
@@ -10533,7 +10537,7 @@
         <v>74</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -10553,10 +10557,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -10579,7 +10583,7 @@
         <v>74</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L90" s="2"/>
       <c r="M90" s="2"/>
@@ -10632,7 +10636,7 @@
         <v>74</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -10652,10 +10656,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -10678,7 +10682,7 @@
         <v>74</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="L91" s="2"/>
       <c r="M91" s="2"/>
@@ -10731,7 +10735,7 @@
         <v>74</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -10751,10 +10755,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -10777,7 +10781,7 @@
         <v>74</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="L92" s="2"/>
       <c r="M92" s="2"/>
@@ -10830,7 +10834,7 @@
         <v>74</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -10850,10 +10854,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -10876,7 +10880,7 @@
         <v>74</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="L93" s="2"/>
       <c r="M93" s="2"/>
@@ -10929,7 +10933,7 @@
         <v>74</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -10949,10 +10953,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -10975,7 +10979,7 @@
         <v>74</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L94" s="2"/>
       <c r="M94" s="2"/>
@@ -11028,7 +11032,7 @@
         <v>74</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -11048,10 +11052,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -11074,7 +11078,7 @@
         <v>74</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="L95" s="2"/>
       <c r="M95" s="2"/>
@@ -11127,7 +11131,7 @@
         <v>74</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -11147,10 +11151,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -11173,7 +11177,7 @@
         <v>74</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="L96" s="2"/>
       <c r="M96" s="2"/>
@@ -11226,7 +11230,7 @@
         <v>74</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -11246,10 +11250,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -11272,7 +11276,7 @@
         <v>74</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="L97" s="2"/>
       <c r="M97" s="2"/>
@@ -11325,7 +11329,7 @@
         <v>74</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -11345,10 +11349,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -11371,11 +11375,11 @@
         <v>74</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L98" s="2"/>
       <c r="M98" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -11426,7 +11430,7 @@
         <v>74</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -11446,10 +11450,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -11547,10 +11551,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -11648,10 +11652,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -11749,10 +11753,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -11850,10 +11854,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -11953,10 +11957,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -12056,10 +12060,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -12159,10 +12163,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -12262,10 +12266,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -12363,10 +12367,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -12400,7 +12404,7 @@
       </c>
       <c r="Q108" s="2"/>
       <c r="R108" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="S108" t="s" s="2">
         <v>74</v>
@@ -12422,7 +12426,7 @@
       </c>
       <c r="Y108" s="2"/>
       <c r="Z108" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>74</v>
@@ -12440,7 +12444,7 @@
         <v>74</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -12460,10 +12464,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -12486,7 +12490,7 @@
         <v>74</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L109" s="2"/>
       <c r="M109" s="2"/>
@@ -12539,7 +12543,7 @@
         <v>74</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>75</v>
@@ -12559,10 +12563,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -12585,7 +12589,7 @@
         <v>74</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L110" s="2"/>
       <c r="M110" s="2"/>
@@ -12638,7 +12642,7 @@
         <v>74</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>

--- a/main/ig/StructureDefinition-fr-cda-dicom-quantite-subordonnee.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-dicom-quantite-subordonnee.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T14:20:03+00:00</t>
+    <t>2026-06-29T15:28:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-dicom-quantite-subordonnee.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-dicom-quantite-subordonnee.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T15:28:29+00:00</t>
+    <t>2026-06-30T08:01:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-dicom-quantite-subordonnee.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-dicom-quantite-subordonnee.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T08:01:58+00:00</t>
+    <t>2026-06-30T09:01:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-dicom-quantite-subordonnee.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-dicom-quantite-subordonnee.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:01:37+00:00</t>
+    <t>2026-06-30T09:56:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-dicom-quantite-subordonnee.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-dicom-quantite-subordonnee.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:56:22+00:00</t>
+    <t>2026-08-06T11:33:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
